--- a/content/Tile_Content_Appendix_B_MONTH_21AUG26.xlsx
+++ b/content/Tile_Content_Appendix_B_MONTH_21AUG26.xlsx
@@ -986,7 +986,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>% TM alerts past closure date</t>
+          <t>% TM alerts past due</t>
         </is>
       </c>
       <c r="H17" s="8" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t># Regulatory Reports Overdue</t>
+          <t># Reg Reports Overdue</t>
         </is>
       </c>
       <c r="H19" s="8" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t># recent Audit and Exam Findings</t>
+          <t># Audit/Exam Findings</t>
         </is>
       </c>
       <c r="H27" s="8" t="n">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t># FCC program initiatives overdue</t>
+          <t># FCC initiatives overdue</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t># KDEs requiring remediation</t>
+          <t># KDEs to remediate</t>
         </is>
       </c>
       <c r="H30" s="8" t="n">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t># model validations overdue</t>
+          <t># model validations due</t>
         </is>
       </c>
       <c r="H31" s="8" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t># information sharing requests overdue</t>
+          <t># info sharing overdue</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>FCC Risk Appetite Statement</t>
+          <t>Risk Appetite Statement</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">

--- a/content/Tile_Content_Appendix_B_MONTH_21AUG26.xlsx
+++ b/content/Tile_Content_Appendix_B_MONTH_21AUG26.xlsx
@@ -2042,7 +2042,7 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Data, models and records</t>
+          <t>Governance and Reporting</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
